--- a/out/LSTM-S4_repeat_3_000002.xlsx
+++ b/out/LSTM-S4_repeat_3_000002.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.199521431067184</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.199521431067184</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,14 +35917,14 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36712,14 +36712,14 @@
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.331838802061187</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-S4_repeat_3_000002.xlsx
+++ b/out/LSTM-S4_repeat_3_000002.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.6725037851595846</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.00247858901595692</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.331838802061187</v>
+        <v>0.1975214109840431</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.599521431067185</v>
+        <v>0.1975214109840431</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.331838802061187</v>
+        <v>0.1975214109840431</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.00247858901595692</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,14 +39097,14 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.6725037851595846</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39892,14 +39892,14 @@
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40687,14 +40687,14 @@
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.6725037851595846</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.00247858901595692</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43079,7 +43079,7 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.331838802061187</v>
+        <v>0.1975214109840431</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4725037851595846</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44662,14 +44662,14 @@
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA55" t="n">
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46252,14 +46252,14 @@
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA57" t="n">
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47842,14 +47842,14 @@
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA59" t="n">
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49432,14 +49432,14 @@
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA61" t="n">
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50227,14 +50227,14 @@
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA62" t="n">
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51022,14 +51022,14 @@
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA63" t="n">
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51817,14 +51817,14 @@
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA64" t="n">
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52612,14 +52612,14 @@
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA65" t="n">
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53407,14 +53407,14 @@
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA66" t="n">
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -54997,14 +54997,14 @@
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA68" t="n">
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56587,14 +56587,14 @@
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA70" t="n">
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57382,14 +57382,14 @@
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA71" t="n">
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58177,14 +58177,14 @@
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA72" t="n">
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59767,14 +59767,14 @@
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA74" t="n">
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61357,14 +61357,14 @@
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA76" t="n">
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA77" t="n">
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA78" t="n">
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.4725037851595845</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66134,7 +66134,7 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.331838802061187</v>
+        <v>0.1975214109840432</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>1.331838802061187</v>
+        <v>0.1975214109840431</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.599521431067185</v>
+        <v>-0.4725037851595846</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.599521431067185</v>
+        <v>-1.142528981303212</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70102,14 +70102,14 @@
       </c>
       <c r="IZ87" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA87" t="n">
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70897,14 +70897,14 @@
       </c>
       <c r="IZ88" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA88" t="n">
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-2.199521431067184</v>
+        <v>-1.342528981303212</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71692,14 +71692,14 @@
       </c>
       <c r="IZ89" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA89" t="n">
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-2.199521431067184</v>
+        <v>-0.6725037851595846</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7318388020611866</v>
+        <v>-0.00247858901595685</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76469,7 +76469,7 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.331838802061187</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.8675466071276708</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85214,7 +85214,7 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7318388020611866</v>
+        <v>0.6675466071276708</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/LSTM-S4_repeat_3_000002.xlsx
+++ b/out/LSTM-S4_repeat_3_000002.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.006627809256315231</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.003806143999099731</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002516068518161774</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.002005618065595627</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.001339506357908249</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.0007662847638130188</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0005522742867469788</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6725037851595846</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0001378841698169708</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.00247858901595692</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.001381278038024902</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.8675466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001128051429986954</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0003661960363388062</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.1975214109840431</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-5.541741847991943e-05</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.1975214109840431</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0001836009323596954</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.1975214109840431</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0003303922712802887</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8675466071276708</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0003898888826370239</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0004776045680046082</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0007454156875610352</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001034624874591827</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001206919550895691</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.001368872821331024</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001419413834810257</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001358270645141602</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001388520002365112</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.00292239710688591</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.003183215856552124</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.002889327704906464</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.002774719148874283</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.002682894468307495</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.002592958509922028</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.002469014376401901</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002579815685749054</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002535909414291382</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.00268196314573288</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.003177840262651443</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.00360395759344101</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004364687949419022</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.004272736608982086</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.003620818257331848</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004074539989233017</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004651598632335663</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.005483008921146393</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.006452605128288269</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005872156471014023</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006893232464790344</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004299379885196686</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38302,14 +38302,14 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.00168817862868309</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.00247858901595692</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0002438575029373169</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6725037851595846</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0008370578289031982</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001336496323347092</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6725037851595846</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0001687519252300262</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.00247858901595692</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.0005161836743354797</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>8.427724242210388e-05</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1975214109840431</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0009450167417526245</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.4725037851595846</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.001887932419776917</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.002215012907981873</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002703290432691574</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.002671327441930771</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.001932412385940552</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48641,10 +48641,10 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.001596502959728241</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.00138285756111145</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.0007604658603668213</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.000916697084903717</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.001634221524000168</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.001618504524230957</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.001119930297136307</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.0005866177380084991</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0008854605257511139</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55796,10 +55796,10 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001983743160963058</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002875760197639465</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003172613680362701</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003126788884401321</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58976,10 +58976,10 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.003083433955907822</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00260775163769722</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.002201922237873077</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.001904744654893875</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.342528981303212</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001486979424953461</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.342528981303212</v>
+        <v>0.3</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.001038379967212677</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.342528981303212</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0006483308970928192</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.342528981303212</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.000433061271905899</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.342528981303212</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65336,10 +65336,10 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.0001608468592166901</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.4725037851595845</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.0001318864524364471</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1975214109840432</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66926,10 +66926,10 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.0003066733479499817</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>6.720051169395447e-05</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1975214109840431</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68516,10 +68516,10 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-9.302049875259399e-05</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.4725037851595846</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.000332612544298172</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.142528981303212</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.0006710775196552277</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.16</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.000456005334854126</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.342528981303212</v>
+        <v>-0.16</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.0003033727407455444</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6725037851595846</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.0003561899065971375</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.00247858901595685</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.0001616552472114563</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>2.367421984672546e-05</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.0003742799162864685</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75671,10 +75671,10 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.0003713518381118774</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76466,10 +76466,10 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.0002662986516952515</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.0003468878567218781</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78056,10 +78056,10 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.00106004998087883</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.001361381262540817</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.001747287809848785</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001908421516418457</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.002178676426410675</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.002056322991847992</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.002136141061782837</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.002362173050642014</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.002320621162652969</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.002321716398000717</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86006,10 +86006,10 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.002350185066461563</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.002281650900840759</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.0021694116294384</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.002241205424070358</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.002168543636798859</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.16</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.002308458089828491</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.00229538232088089</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.002403486520051956</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.002420477569103241</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.002577349543571472</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.003697704523801804</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.004094135016202927</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.005548372864723206</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.004990249872207642</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.004786886274814606</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6675466071276708</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.003672022372484207</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.002664331346750259</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.3</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.002444587647914886</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.002058207988739014</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.51</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.002729233354330063</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.6675466071276708</v>
+        <v>-0.58</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>
